--- a/FPE/Outputs/cruces_ideam_genero_estrato_motivo_tiempo.xlsx
+++ b/FPE/Outputs/cruces_ideam_genero_estrato_motivo_tiempo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/FPE/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_CC51B936EF40F69BB55EFFED80528BB207F8B23F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{430C5E1D-9029-432F-BAA2-AD158BF06B45}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_EDD999268AB6FD90B7ECF2E830F0862F2FFF922E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C2CBF2-1F9D-431D-A9A3-1CAC8D11BC9D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6204" yWindow="3804" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tiempo_ciudad_genero" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="26">
   <si>
     <t>ciudad</t>
   </si>
@@ -71,40 +71,25 @@
     <t>Trabajo</t>
   </si>
   <si>
-    <t>Recreación, salud y actividades personales</t>
+    <t>Salud</t>
   </si>
   <si>
-    <t>Compras y trámites</t>
+    <t>Viajes de cuidado</t>
+  </si>
+  <si>
+    <t>Recreación y actividades personales</t>
   </si>
   <si>
     <t>Estudio</t>
+  </si>
+  <si>
+    <t>Trámites</t>
   </si>
   <si>
     <t>Visitas sociales</t>
   </si>
   <si>
     <t>Otro</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (escuela, niñas/os)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (persona enferma)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (salud, niñas/os)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (persona con discapacidad)</t>
-  </si>
-  <si>
-    <t>Cuidado y familia (recreación, niñas/os)</t>
   </si>
   <si>
     <t>p9_estrato3</t>
@@ -180,6 +165,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -609,11 +598,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -661,10 +649,10 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0.169811320754717</v>
+        <v>0.1132075471698113</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -678,10 +666,10 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>0.1037735849056604</v>
+        <v>7.5471698113207544E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -695,10 +683,10 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>4.2452830188679243E-2</v>
+        <v>5.6603773584905662E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -712,10 +700,10 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>2.358490566037736E-2</v>
+        <v>4.2452830188679243E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -729,10 +717,10 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>1.886792452830189E-2</v>
+        <v>2.8301886792452831E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -740,16 +728,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>0.48416289592760181</v>
+        <v>2.358490566037736E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -757,16 +745,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>0.26244343891402722</v>
+        <v>1.886792452830189E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,13 +765,13 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="E10">
-        <v>0.14932126696832579</v>
+        <v>0.48416289592760181</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -794,13 +782,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E11">
-        <v>5.8823529411764712E-2</v>
+        <v>0.23981900452488689</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -811,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>2.2624434389140271E-2</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -828,13 +816,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E13">
-        <v>1.357466063348416E-2</v>
+        <v>5.8823529411764712E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -845,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>4.5248868778280547E-3</v>
+        <v>4.9773755656108587E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -862,47 +850,47 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>4.5248868778280547E-3</v>
+        <v>2.2624434389140271E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D16">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>0.5957446808510638</v>
+        <v>2.2624434389140271E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>0.1223404255319149</v>
+        <v>4.5248868778280547E-3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -913,13 +901,13 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E18">
-        <v>0.1117021276595745</v>
+        <v>0.5957446808510638</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -930,13 +918,13 @@
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>0.1063829787234043</v>
+        <v>0.1117021276595745</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -947,13 +935,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>4.2553191489361701E-2</v>
+        <v>0.1063829787234043</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -964,13 +952,13 @@
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E21">
-        <v>5.3191489361702126E-3</v>
+        <v>8.5106382978723402E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -981,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>5.3191489361702126E-3</v>
+        <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -998,13 +986,13 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>5.3191489361702126E-3</v>
+        <v>3.7234042553191488E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1015,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>5.3191489361702126E-3</v>
+        <v>1.5957446808510641E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1029,16 +1017,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D25">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0.39047619047619048</v>
+        <v>5.3191489361702126E-3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1049,13 +1037,13 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>0.31904761904761902</v>
+        <v>0.39047619047619048</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1066,13 +1054,13 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E27">
-        <v>0.15238095238095239</v>
+        <v>0.28095238095238101</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1083,13 +1071,13 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E28">
-        <v>5.7142857142857141E-2</v>
+        <v>0.14285714285714279</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1103,10 +1091,10 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>3.8095238095238099E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1117,13 +1105,13 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>1.9047619047619049E-2</v>
+        <v>4.2857142857142858E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1134,13 +1122,13 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>9.5238095238095247E-3</v>
+        <v>3.8095238095238099E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1151,13 +1139,13 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>4.7619047619047623E-3</v>
+        <v>3.8095238095238099E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1168,30 +1156,13 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>4.7619047619047623E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>4.7619047619047623E-3</v>
+        <v>9.5238095238095247E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1201,11 +1172,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="47.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1241,28 +1209,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>52.5</v>
+        <v>127.7777777777778</v>
       </c>
       <c r="F2">
-        <v>52.5</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>22.5</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="I2">
-        <v>90</v>
+        <v>231.9999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1270,28 +1238,28 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>45.757575757575758</v>
+        <v>63.615384615384613</v>
       </c>
       <c r="F3">
+        <v>56</v>
+      </c>
+      <c r="G3">
         <v>30</v>
       </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
       <c r="H3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I3">
-        <v>88</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1299,28 +1267,28 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="H4">
-        <v>17.5</v>
+        <v>40.75</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>60.100000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1337,19 +1305,19 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="F5">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1363,22 +1331,22 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>127.7777777777778</v>
+        <v>38.5</v>
       </c>
       <c r="F6">
+        <v>22.5</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
         <v>45</v>
       </c>
-      <c r="G6">
-        <v>40</v>
-      </c>
-      <c r="H6">
-        <v>120</v>
-      </c>
       <c r="I6">
-        <v>231.9999999999996</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1392,22 +1360,22 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>63.615384615384613</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="H7">
-        <v>80</v>
-      </c>
       <c r="I7">
-        <v>113.4</v>
+        <v>47.999999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1415,28 +1383,28 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>54.791666666666657</v>
       </c>
       <c r="F8">
-        <v>22.5</v>
+        <v>44</v>
       </c>
       <c r="G8">
-        <v>11.75</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>40.75</v>
+        <v>86.25</v>
       </c>
       <c r="I8">
-        <v>60.100000000000009</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1444,28 +1412,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="E9">
-        <v>230</v>
+        <v>64.566037735849051</v>
       </c>
       <c r="F9">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="H9">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="I9">
-        <v>230</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1473,28 +1441,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="E10">
-        <v>49.361111111111107</v>
+        <v>42.764705882352942</v>
       </c>
       <c r="F10">
         <v>30</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="H10">
-        <v>86.25</v>
+        <v>60</v>
       </c>
       <c r="I10">
-        <v>106.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1502,28 +1470,28 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="E11">
-        <v>61.586206896551722</v>
+        <v>60.439252336448597</v>
       </c>
       <c r="F11">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I11">
-        <v>132.4</v>
+        <v>126.0000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1531,25 +1499,25 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>42.764705882352942</v>
+        <v>72.5</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>67.5</v>
       </c>
       <c r="G12">
-        <v>18.75</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I12">
         <v>97.5</v>
@@ -1560,28 +1528,28 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>60.439252336448597</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I13">
-        <v>126.0000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1589,28 +1557,28 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E14">
+        <v>45</v>
+      </c>
+      <c r="F14">
         <v>35</v>
-      </c>
-      <c r="F14">
-        <v>15</v>
       </c>
       <c r="G14">
         <v>15</v>
       </c>
       <c r="H14">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I14">
-        <v>78.999999999999972</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1618,86 +1586,86 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>26.2</v>
+        <v>44.884615384615387</v>
       </c>
       <c r="F15">
         <v>30</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>16.25</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="I15">
-        <v>33.4</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>49.55</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>31.5</v>
+        <v>15</v>
       </c>
       <c r="H16">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I16">
-        <v>74.100000000000023</v>
+        <v>78.999999999999972</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>49.875</v>
+        <v>26.2</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G17">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H17">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I17">
-        <v>70.600000000000009</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1705,28 +1673,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>36.952380952380949</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1734,28 +1702,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>23.75</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>17.5</v>
+        <v>39</v>
       </c>
       <c r="G19">
-        <v>13.75</v>
+        <v>18.75</v>
       </c>
       <c r="H19">
-        <v>27.5</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>41</v>
+        <v>58.900000000000013</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1763,28 +1731,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1792,28 +1760,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>22.5</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>22.5</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>18.75</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>26.25</v>
       </c>
       <c r="I21">
-        <v>35</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1821,28 +1789,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="G22">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H22">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I22">
-        <v>65</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1850,28 +1818,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>50.125</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>42.5</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>82.5</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1879,28 +1847,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>39</v>
+        <v>52.75</v>
       </c>
       <c r="F24">
-        <v>39</v>
+        <v>57.5</v>
       </c>
       <c r="G24">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="H24">
-        <v>39</v>
+        <v>68.5</v>
       </c>
       <c r="I24">
-        <v>39</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1908,28 +1876,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E25">
-        <v>36.952380952380949</v>
+        <v>46.745762711864408</v>
       </c>
       <c r="F25">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G25">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H25">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I25">
-        <v>64</v>
+        <v>75.000000000000028</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1937,28 +1905,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="E26">
-        <v>36</v>
+        <v>45.955357142857153</v>
       </c>
       <c r="F26">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G26">
-        <v>18.75</v>
+        <v>30</v>
       </c>
       <c r="H26">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I26">
-        <v>58.900000000000013</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -1966,28 +1934,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>49.073170731707307</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G27">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="H27">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>84.100000000000051</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -1998,25 +1966,25 @@
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>22.5</v>
+        <v>58.142857142857153</v>
       </c>
       <c r="F28">
-        <v>22.5</v>
+        <v>65</v>
       </c>
       <c r="G28">
-        <v>18.75</v>
+        <v>54</v>
       </c>
       <c r="H28">
-        <v>26.25</v>
+        <v>65</v>
       </c>
       <c r="I28">
-        <v>28.5</v>
+        <v>65.800000000000011</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -2024,28 +1992,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>54.478260869565219</v>
+        <v>42</v>
       </c>
       <c r="F29">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G29">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H29">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I29">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -2053,28 +2021,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>16</v>
+      </c>
+      <c r="E30">
+        <v>40.25</v>
+      </c>
+      <c r="F30">
+        <v>33.5</v>
+      </c>
+      <c r="G30">
         <v>15</v>
       </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>67</v>
-      </c>
-      <c r="E30">
-        <v>47.149253731343293</v>
-      </c>
-      <c r="F30">
-        <v>45</v>
-      </c>
-      <c r="G30">
-        <v>30</v>
-      </c>
       <c r="H30">
-        <v>60.5</v>
+        <v>54</v>
       </c>
       <c r="I30">
-        <v>85.799999999999983</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -2082,28 +2050,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="E31">
-        <v>45.955357142857153</v>
+        <v>47.56666666666667</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="G31">
         <v>30</v>
       </c>
       <c r="H31">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="I31">
-        <v>80</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -2111,28 +2079,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>49.073170731707307</v>
+        <v>32.125</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>31.5</v>
+        <v>13.75</v>
       </c>
       <c r="H32">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I32">
-        <v>84.100000000000051</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -2140,56 +2108,27 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33">
-        <v>32.125</v>
+        <v>35</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G33">
-        <v>13.75</v>
+        <v>20</v>
       </c>
       <c r="H33">
-        <v>45</v>
+        <v>44.25</v>
       </c>
       <c r="I33">
-        <v>68.099999999999994</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>8</v>
-      </c>
-      <c r="E34">
-        <v>35</v>
-      </c>
-      <c r="F34">
-        <v>30</v>
-      </c>
-      <c r="G34">
-        <v>20</v>
-      </c>
-      <c r="H34">
-        <v>44.25</v>
-      </c>
-      <c r="I34">
         <v>59.7</v>
       </c>
     </row>
@@ -2200,15 +2139,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>12</v>
@@ -2225,7 +2168,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -2242,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>0.30128205128205132</v>
+        <v>0.24358974358974361</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2259,16 +2202,16 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>0.108974358974359</v>
+        <v>9.6153846153846159E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2276,16 +2219,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>3.8461538461538457E-2</v>
+        <v>5.7692307692307702E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2293,16 +2236,16 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>2.564102564102564E-2</v>
+        <v>3.8461538461538457E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2310,16 +2253,16 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>1.282051282051282E-2</v>
+        <v>2.564102564102564E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2327,16 +2270,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>1.282051282051282E-2</v>
+        <v>2.564102564102564E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2344,16 +2287,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0.57754010695187163</v>
+        <v>1.282051282051282E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2361,16 +2304,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="E10">
-        <v>0.1764705882352941</v>
+        <v>0.57754010695187163</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2378,16 +2321,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>0.13903743315508019</v>
+        <v>0.1497326203208556</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2395,16 +2338,16 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
         <v>17</v>
       </c>
-      <c r="D12">
-        <v>11</v>
-      </c>
       <c r="E12">
-        <v>5.8823529411764712E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2412,16 +2355,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>3.2085561497326207E-2</v>
+        <v>5.8823529411764712E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2429,16 +2372,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>5.3475935828877002E-3</v>
+        <v>5.8823529411764712E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2446,16 +2389,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>5.3475935828877002E-3</v>
+        <v>3.2085561497326207E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2463,16 +2406,16 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>5.3475935828877002E-3</v>
+        <v>2.6737967914438499E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2480,16 +2423,16 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>0.6333333333333333</v>
+        <v>5.3475935828877002E-3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2497,16 +2440,16 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>0.15555555555555561</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2514,16 +2457,16 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19">
-        <v>0.1333333333333333</v>
+        <v>0.1222222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2531,16 +2474,16 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>5.5555555555555552E-2</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -2548,67 +2491,67 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>2.222222222222222E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D22">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>0.44751381215469621</v>
+        <v>3.3333333333333333E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>0.23204419889502759</v>
+        <v>2.222222222222222E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>0.14917127071823211</v>
+        <v>2.222222222222222E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2616,16 +2559,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="E25">
-        <v>7.7348066298342538E-2</v>
+        <v>0.44751381215469621</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2633,16 +2576,16 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>5.5248618784530378E-2</v>
+        <v>0.19889502762430941</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2650,16 +2593,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27">
         <v>22</v>
       </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
       <c r="E27">
-        <v>1.6574585635359119E-2</v>
+        <v>0.1215469613259668</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2667,16 +2610,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>5.5248618784530376E-3</v>
+        <v>7.7348066298342538E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2684,16 +2627,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E29">
-        <v>5.5248618784530376E-3</v>
+        <v>6.0773480662983423E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2701,16 +2644,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>5.5248618784530376E-3</v>
+        <v>5.5248618784530378E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2718,16 +2661,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>5.5248618784530376E-3</v>
+        <v>3.3149171270718231E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2735,16 +2678,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D32">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.46583850931677018</v>
+        <v>5.5248618784530376E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2752,16 +2695,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E33">
-        <v>0.2484472049689441</v>
+        <v>0.46583850931677018</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2769,16 +2712,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E34">
-        <v>0.13043478260869559</v>
+        <v>0.21739130434782611</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2786,16 +2729,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E35">
-        <v>8.6956521739130432E-2</v>
+        <v>0.13664596273291929</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2803,16 +2746,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>3.7267080745341623E-2</v>
+        <v>8.6956521739130432E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2820,16 +2763,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>1.2422360248447201E-2</v>
+        <v>3.7267080745341623E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2837,16 +2780,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>1.2422360248447201E-2</v>
+        <v>3.1055900621118009E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2854,16 +2797,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>6.2111801242236021E-3</v>
+        <v>1.2422360248447201E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2871,16 +2814,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D40">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>0.6785714285714286</v>
+        <v>1.2422360248447201E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2888,16 +2831,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E41">
-        <v>0.14285714285714279</v>
+        <v>0.6785714285714286</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2905,16 +2848,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>8.9285714285714288E-2</v>
+        <v>0.14285714285714279</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2922,16 +2865,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>7.1428571428571425E-2</v>
+        <v>8.9285714285714288E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2939,16 +2882,33 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>1.785714285714286E-2</v>
+        <v>5.3571428571428568E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2958,11 +2918,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2973,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -2993,7 +2953,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -3013,16 +2973,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0.26027397260273971</v>
+        <v>0.15068493150684931</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -3033,16 +2993,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>8.2191780821917804E-2</v>
+        <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -3053,16 +3013,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4.1095890410958902E-2</v>
+        <v>8.2191780821917804E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3073,16 +3033,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>2.7397260273972601E-2</v>
+        <v>4.1095890410958902E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -3093,16 +3053,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1.3698630136986301E-2</v>
+        <v>2.7397260273972601E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3113,16 +3073,16 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0.64948453608247425</v>
+        <v>1.3698630136986301E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3133,16 +3093,16 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="F9">
-        <v>0.134020618556701</v>
+        <v>0.64948453608247425</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3153,16 +3113,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>0.1237113402061856</v>
+        <v>0.1134020618556701</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3173,16 +3133,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>4.1237113402061848E-2</v>
+        <v>8.247422680412371E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3193,16 +3153,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>4.1237113402061848E-2</v>
+        <v>5.1546391752577317E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3213,16 +3173,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>1.030927835051546E-2</v>
+        <v>4.1237113402061848E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3233,16 +3193,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>0.73809523809523814</v>
+        <v>4.1237113402061848E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3253,16 +3213,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>0.119047619047619</v>
+        <v>1.030927835051546E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3273,16 +3233,16 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>7.1428571428571425E-2</v>
+        <v>1.030927835051546E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3293,16 +3253,16 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>4.7619047619047623E-2</v>
+        <v>0.73809523809523814</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3313,16 +3273,16 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>2.3809523809523812E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3330,19 +3290,19 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>0.43373493975903621</v>
+        <v>4.7619047619047623E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -3350,19 +3310,19 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>0.33734939759036142</v>
+        <v>4.7619047619047623E-2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -3370,19 +3330,19 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>0.13253012048192769</v>
+        <v>4.7619047619047623E-2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -3390,19 +3350,19 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3.614457831325301E-2</v>
+        <v>2.3809523809523812E-2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3410,19 +3370,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3.614457831325301E-2</v>
+        <v>2.3809523809523812E-2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3433,16 +3393,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>2.4096385542168679E-2</v>
+        <v>0.43373493975903621</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -3453,16 +3413,16 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>0.5</v>
+        <v>0.3253012048192771</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -3473,16 +3433,16 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>0.23333333333333331</v>
+        <v>0.108433734939759</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3493,16 +3453,16 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>0.1444444444444444</v>
+        <v>4.8192771084337352E-2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3513,16 +3473,16 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>7.7777777777777779E-2</v>
+        <v>3.614457831325301E-2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3533,16 +3493,16 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>2.222222222222222E-2</v>
+        <v>3.614457831325301E-2</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3553,16 +3513,16 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>1.111111111111111E-2</v>
+        <v>1.204819277108434E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -3573,16 +3533,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F31">
-        <v>1.111111111111111E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -3593,16 +3553,16 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>0.54166666666666663</v>
+        <v>0.18888888888888891</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -3613,7 +3573,7 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -3622,7 +3582,7 @@
         <v>9</v>
       </c>
       <c r="F33">
-        <v>0.1875</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3633,16 +3593,16 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>0.1875</v>
+        <v>7.7777777777777779E-2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -3653,16 +3613,16 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>6.25E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -3673,147 +3633,147 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>2.0833333333333329E-2</v>
+        <v>4.4444444444444453E-2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E37">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>0.56321839080459768</v>
+        <v>2.222222222222222E-2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F38">
-        <v>0.12643678160919539</v>
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>0.1149425287356322</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>0.1149425287356322</v>
+        <v>0.16666666666666671</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>5.7471264367816091E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>1.149425287356322E-2</v>
+        <v>2.0833333333333329E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -3822,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>1.149425287356322E-2</v>
+        <v>2.0833333333333329E-2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3833,16 +3793,16 @@
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
       </c>
       <c r="E44">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F44">
-        <v>0.57333333333333336</v>
+        <v>0.56321839080459768</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -3853,16 +3813,16 @@
         <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>0.1466666666666667</v>
+        <v>0.1149425287356322</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3873,16 +3833,16 @@
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>0.12</v>
+        <v>0.1149425287356322</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -3893,16 +3853,16 @@
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47">
-        <v>0.1066666666666667</v>
+        <v>8.0459770114942528E-2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3913,16 +3873,16 @@
         <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>0.04</v>
+        <v>5.7471264367816091E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3933,16 +3893,16 @@
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>1.3333333333333331E-2</v>
+        <v>4.5977011494252873E-2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3953,16 +3913,16 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E50">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>0.76923076923076927</v>
+        <v>1.149425287356322E-2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3973,16 +3933,16 @@
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>0.1153846153846154</v>
+        <v>1.149425287356322E-2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -3993,16 +3953,16 @@
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F52">
-        <v>3.8461538461538457E-2</v>
+        <v>0.57333333333333336</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -4013,16 +3973,16 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>3.8461538461538457E-2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -4033,16 +3993,16 @@
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F54">
-        <v>3.8461538461538457E-2</v>
+        <v>0.1066666666666667</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4050,19 +4010,19 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E55">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F55">
-        <v>0.34042553191489361</v>
+        <v>0.1066666666666667</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -4070,19 +4030,19 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E56">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>0.32978723404255322</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -4090,19 +4050,19 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E57">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>0.18085106382978719</v>
+        <v>2.6666666666666668E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4110,19 +4070,19 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>5.3191489361702128E-2</v>
+        <v>2.6666666666666668E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4130,19 +4090,19 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F59">
-        <v>4.2553191489361701E-2</v>
+        <v>0.76923076923076927</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4150,19 +4110,19 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>2.1276595744680851E-2</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4170,19 +4130,19 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <v>1.063829787234043E-2</v>
+        <v>3.8461538461538457E-2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -4190,19 +4150,19 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>1.063829787234043E-2</v>
+        <v>3.8461538461538457E-2</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -4210,19 +4170,19 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>1.063829787234043E-2</v>
+        <v>3.8461538461538457E-2</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -4233,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -4242,7 +4202,7 @@
         <v>32</v>
       </c>
       <c r="F64">
-        <v>0.37209302325581389</v>
+        <v>0.34042553191489361</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -4253,16 +4213,16 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>15</v>
       </c>
       <c r="E65">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65">
-        <v>0.33720930232558138</v>
+        <v>0.27659574468085107</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -4273,16 +4233,16 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>16</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F66">
-        <v>0.1395348837209302</v>
+        <v>0.15957446808510639</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -4293,16 +4253,16 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67">
-        <v>6.9767441860465115E-2</v>
+        <v>7.4468085106382975E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -4313,16 +4273,16 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>3.4883720930232558E-2</v>
+        <v>5.3191489361702128E-2</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4333,16 +4293,16 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F69">
-        <v>2.3255813953488368E-2</v>
+        <v>5.3191489361702128E-2</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -4353,16 +4313,16 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>2.3255813953488368E-2</v>
+        <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -4373,16 +4333,16 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
       </c>
       <c r="E71">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F71">
-        <v>0.6</v>
+        <v>0.37209302325581389</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -4393,16 +4353,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
         <v>15</v>
       </c>
       <c r="E72">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F72">
-        <v>0.23333333333333331</v>
+        <v>0.30232558139534882</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -4413,16 +4373,16 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D73" t="s">
         <v>16</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F73">
-        <v>0.1</v>
+        <v>0.16279069767441859</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -4433,16 +4393,176 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <v>6.9767441860465115E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
         <v>17</v>
       </c>
-      <c r="E74">
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75">
+        <v>3.4883720930232558E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>3.4883720930232558E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77">
         <v>2</v>
       </c>
-      <c r="F74">
+      <c r="F77">
+        <v>2.3255813953488368E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78">
+        <v>18</v>
+      </c>
+      <c r="F78">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79">
+        <v>7</v>
+      </c>
+      <c r="F79">
+        <v>0.23333333333333331</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80">
         <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81">
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>3.3333333333333333E-2</v>
       </c>
     </row>
   </sheetData>
